--- a/vendor-performance/datasets/vendor-fulfillment-events.xlsx
+++ b/vendor-performance/datasets/vendor-fulfillment-events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e29a6debf5eaf8e/Documents/GitHub/northstar-health-operations/vendor-performance/datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{781A5740-F98B-466B-9BC1-6BE5C0F2C618}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95748311-0328-49B7-B180-EF8EEE3232E3}"/>
   <bookViews>
     <workbookView xWindow="2685" yWindow="2685" windowWidth="23475" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="65">
   <si>
     <t>fulfillment_event_id</t>
   </si>
@@ -545,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -620,214 +620,211 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46163</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46165</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46165</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="K2">
+        <v>60</v>
+      </c>
+      <c r="L2">
+        <v>60</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="U2" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F3" s="1">
         <v>46163</v>
       </c>
       <c r="G3" s="1">
-        <v>46165</v>
-      </c>
-      <c r="H3" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="S3" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T3" t="s">
+        <v>42</v>
       </c>
       <c r="U3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F4" s="1">
         <v>46163</v>
       </c>
       <c r="G4" s="1">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K4">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
       </c>
       <c r="N4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="S4" t="b">
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="U4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1">
         <v>46163</v>
       </c>
       <c r="G5" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="I5" t="s">
         <v>51</v>
@@ -836,7 +833,7 @@
         <v>51</v>
       </c>
       <c r="K5">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -860,51 +857,51 @@
         <v>32</v>
       </c>
       <c r="S5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" t="s">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="U5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="G6" s="1">
-        <v>46166</v>
+        <v>46164</v>
+      </c>
+      <c r="H6" s="1">
+        <v>46164</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -919,139 +916,77 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F7" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="G7" s="1">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="H7" s="1">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K7">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L7">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="M7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="S7" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T7" t="s">
+        <v>63</v>
       </c>
       <c r="U7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46163</v>
-      </c>
-      <c r="G8" s="1">
-        <v>46165</v>
-      </c>
-      <c r="H8" s="1">
-        <v>46166</v>
-      </c>
-      <c r="I8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8">
-        <v>50</v>
-      </c>
-      <c r="L8">
-        <v>35</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8" t="s">
-        <v>36</v>
-      </c>
-      <c r="S8" t="b">
-        <v>1</v>
-      </c>
-      <c r="T8" t="s">
-        <v>63</v>
-      </c>
-      <c r="U8" t="s">
         <v>64</v>
       </c>
     </row>
